--- a/bridge-search/BRIDGE-SEARCH-0006_10_GALAXIES.xlsx
+++ b/bridge-search/BRIDGE-SEARCH-0006_10_GALAXIES.xlsx
@@ -532,47 +532,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PGC31036</t>
+          <t>PGC 90695</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RC3</t>
+          <t>HECATE v1.1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>157.800000 72.100000</t>
+          <t>57.312081 16.084660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.02231210 / 311.67 million ly</t>
+          <t>0.02128372 / 287.88 million ly</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GiG [SIMBAD classification]</t>
+          <t>LSB [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1.130 arcmin [catalog value]</t>
+          <t>0.727 × 0.116 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>6,689.0 km/s</t>
+          <t>6,380.7 km/s</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>EST [102.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [60.9 × 9.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -587,34 +587,34 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>EST [simple Hubble-law distance; verify independently]</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>RC3; SIMBAD; values marked EST require verification</t>
+          <t>HECATE v1.1; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>70% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>88% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PGC 1496412</t>
+          <t>PGC 3096784</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC</t>
+          <t>HECATE v1.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57.827500 15.920000</t>
+          <t>37.995000 22.765284</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Not available / Not available</t>
+          <t>0.03266927 / 448.27 million ly</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.480 arcmin [catalog value]</t>
+          <t>0.300 × 0.180 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>9,794.0 km/s</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [39.1 × 23.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -664,19 +664,19 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC; SIMBAD; values marked EST require verification</t>
+          <t>HECATE v1.1; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>42% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>80% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NGC  1023</t>
+          <t>NGC  3504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -686,42 +686,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40.100417 39.062778</t>
+          <t>165.795000 27.973611</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EST [typically old-dominated stellar population, roughly 9–13 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.00200472 / 28.00 million ly</t>
+          <t>0.00506350 / 70.73 million ly</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.940 arcmin [catalog value]</t>
+          <t>1.430 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>601.0 km/s</t>
+          <t>1,518.0 km/s</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>EST [15.8 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [29.4 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10.350 [catalog photometry; band must be shown in viewer]</t>
+          <t>11.820 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -748,17 +748,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGC 14937</t>
+          <t>PGC31027</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HECATE v1.1</t>
+          <t>RC3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65.333179 36.760135</t>
+          <t>157.750000 78.850000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.00819901 / 113.09 million ly</t>
+          <t>0.00934980 / 130.60 million ly</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -778,17 +778,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1.163 × 0.256 arcmin [catalog value; band/isophote may vary]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,458.0 km/s</t>
+          <t>2,789.9 km/s</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>EST [38.3 × 8.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [39.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -803,64 +803,64 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>HECATE v1.1; SIMBAD; values marked EST require verification</t>
+          <t>RC3; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>72% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IC273                 UGC2425               MCG0-08-052           CGCG389-52            IRAS02546+0234</t>
+          <t>NGC  3394</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC</t>
+          <t>RC3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44.295000 2.775556</t>
+          <t>162.662500 65.727500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Not available / Not available</t>
+          <t>0.01135119 / 158.56 million ly</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>GiP [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1.180 arcmin [catalog value]</t>
+          <t>1.280 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>3,403.0 km/s</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [59.0 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -875,69 +875,69 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC; values marked EST require verification</t>
+          <t>RC3; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>78% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IC1894                CGCG464-6             NPM1G+19.0105</t>
+          <t>PGC23700</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC</t>
+          <t>RC3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47.605833 19.606667</t>
+          <t>126.775000 21.650000</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Not available / Not available</t>
+          <t>0.02529750 / 353.37 million ly</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.890 arcmin [catalog value]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>7,584.0 km/s</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [106.9 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>14.100 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -947,34 +947,34 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>HyperLEDA PGC; values marked EST require verification</t>
+          <t>RC3; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>86% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGC 11640</t>
+          <t>PGC 175756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>HECATE v1.1</t>
+          <t>HyperLEDA PGC</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46.524666 41.725333</t>
+          <t>45.453333 2.059722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -984,27 +984,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.01200164 / 170.76 million ly</t>
+          <t>0.10211100 / 1426.33 million ly</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.373 × 0.336 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.520 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,598.0 km/s</t>
+          <t>29,056.5 km/s</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>EST [18.5 × 16.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [215.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1019,24 +1019,24 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>HECATE v1.1; SIMBAD; values marked EST require verification</t>
+          <t>HyperLEDA PGC; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>64% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PGC 1316867</t>
+          <t>PGC 1477525</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37.859583 7.233056</t>
+          <t>53.344583 15.182778</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.620 arcmin [catalog value]</t>
+          <t>0.390 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,22 +1108,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PGC31098</t>
+          <t>PGC 1512559</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RC3</t>
+          <t>HyperLEDA PGC</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>157.975000 77.800000</t>
+          <t>58.692083 16.599167</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EST [mixed/younger stellar populations possible, broadly 1–10 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1.120 arcmin [catalog value]</t>
+          <t>0.420 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1168,19 +1168,19 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>RC3; SIMBAD; values marked EST require verification</t>
+          <t>HyperLEDA PGC; SIMBAD; values marked EST require verification</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50% [completeness + multi-source agreement; not a scientific certainty score]</t>
+          <t>42% [completeness + multi-source agreement; not a scientific certainty score]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGC 3095597</t>
+          <t>PGC 1397822</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40.560833 5.510000</t>
+          <t>38.649583 11.723056</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.06965624 / 972.99 million ly</t>
+          <t>0.02686576 / 375.27 million ly</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sy1 [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0.243 × 0.204 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.880 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,156.8 km/s</t>
+          <t>7,946.0 km/s</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>EST [68.8 × 57.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [96.1 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1355,13 +1355,13 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PGC31036</t>
+          <t>PGC 90695</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>157.800000 72.100000</t>
+          <t>57.312081 16.084660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -1379,13 +1379,13 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PGC 1496412</t>
+          <t>PGC 3096784</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57.827500 15.920000</t>
+          <t>37.995000 22.765284</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -1403,13 +1403,13 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NGC  1023</t>
+          <t>NGC  3504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40.100417 39.062778</t>
+          <t>165.795000 27.973611</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGC 14937</t>
+          <t>PGC31027</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65.333179 36.760135</t>
+          <t>157.750000 78.850000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -1451,13 +1451,13 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IC273                 UGC2425               MCG0-08-052           CGCG389-52            IRAS02546+0234</t>
+          <t>NGC  3394</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44.295000 2.775556</t>
+          <t>162.662500 65.727500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1475,13 +1475,13 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IC1894                CGCG464-6             NPM1G+19.0105</t>
+          <t>PGC23700</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47.605833 19.606667</t>
+          <t>126.775000 21.650000</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGC 11640</t>
+          <t>PGC 175756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46.524666 41.725333</t>
+          <t>45.453333 2.059722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PGC 1316867</t>
+          <t>PGC 1477525</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37.859583 7.233056</t>
+          <t>53.344583 15.182778</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -1547,13 +1547,13 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PGC31098</t>
+          <t>PGC 1512559</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>157.975000 77.800000</t>
+          <t>58.692083 16.599167</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -1571,13 +1571,13 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGC 3095597</t>
+          <t>PGC 1397822</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40.560833 5.510000</t>
+          <t>38.649583 11.723056</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -1698,13 +1698,13 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PGC31036</t>
+          <t>PGC 90695</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>157.800000 72.100000</t>
+          <t>57.312081 16.084660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -1722,24 +1722,16 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1496412</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>HyperLEDA targeted backup</t>
-        </is>
-      </c>
+          <t>PGC 3096784</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57.827500 15.920000</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>EST [broad 5–12 billion year stellar-population range; not an object-specific measurement]</t>
-        </is>
-      </c>
+          <t>37.995000 22.765284</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
@@ -1748,23 +1740,19 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>HyperLEDA targeted backup</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NGC  1023</t>
+          <t>NGC  3504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40.100417 39.062778</t>
+          <t>165.795000 27.973611</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -1782,13 +1770,13 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGC 14937</t>
+          <t>PGC31027</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65.333179 36.760135</t>
+          <t>157.750000 78.850000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -1806,109 +1794,61 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>HECATE targeted backup</t>
-        </is>
-      </c>
+          <t>NGC  3394</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44.295000 2.775556</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>EST [broad 5–12 billion year stellar-population range; not an object-specific measurement]</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0.01056965 / 116.80 million ly</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Early spiral / S0-a galaxy [de Vaucouleurs T=0.9]</t>
-        </is>
-      </c>
+          <t>162.662500 65.727500</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,168.7 km/s</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>HECATE targeted backup</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>HECATE targeted backup</t>
-        </is>
-      </c>
+          <t>PGC23700</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47.605833 19.606667</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>EST [typically old-dominated stellar population, broadly 9–13 billion years; morphology-based]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0.03493417 / 475.06 million ly</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Lenticular galaxy [de Vaucouleurs T=-2.0]</t>
-        </is>
-      </c>
+          <t>126.775000 21.650000</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,473.0 km/s</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>HECATE targeted backup</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGC 11640</t>
+          <t>PGC 175756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46.524666 41.725333</t>
+          <t>45.453333 2.059722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1926,7 +1866,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1316867</t>
+          <t>1477525</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1936,7 +1876,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37.859583 7.233056</t>
+          <t>53.344583 15.182778</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1962,16 +1902,24 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PGC31098</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
+          <t>1512559</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>HyperLEDA targeted backup</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>157.975000 77.800000</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>58.692083 16.599167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>EST [broad 5–12 billion year stellar-population range; not an object-specific measurement]</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1980,19 +1928,23 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>HyperLEDA targeted backup</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGC 3095597</t>
+          <t>PGC 1397822</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40.560833 5.510000</t>
+          <t>38.649583 11.723056</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -2113,7 +2065,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PGC31036</t>
+          <t>PGC 90695</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2123,37 +2075,37 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>157.800000 72.100000</t>
+          <t>57.312081 16.084660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.02231210 / 311.67 million ly</t>
+          <t>0.02128372 / 287.88 million ly</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GiG [SIMBAD classification]</t>
+          <t>LSB [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1.130 arcmin [catalog value]</t>
+          <t>0.727 × 0.116 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>6,689.0 km/s</t>
+          <t>6,380.7 km/s</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>EST [102.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [60.9 × 9.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -2168,7 +2120,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>EST [simple Hubble-law distance; verify independently]</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2185,7 +2137,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PGC 1496412</t>
+          <t>PGC 3096784</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2195,7 +2147,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57.827500 15.920000</t>
+          <t>37.995000 22.765284</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2205,7 +2157,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>0.03266927 / 448.27 million ly</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2215,17 +2167,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.480 arcmin [catalog value]</t>
+          <t>0.300 × 0.180 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>9,794.0 km/s</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [39.1 × 23.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -2250,14 +2202,14 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>69% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>78% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NGC  1023</t>
+          <t>NGC  3504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2267,42 +2219,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40.100417 39.062778</t>
+          <t>165.795000 27.973611</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EST [typically old-dominated stellar population, roughly 9–13 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.00200472 / 28.00 million ly</t>
+          <t>0.00506350 / 70.73 million ly</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.940 arcmin [catalog value]</t>
+          <t>1.430 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>601.0 km/s</t>
+          <t>1,518.0 km/s</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>EST [15.8 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [29.4 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10.350 [catalog photometry; band must be shown in viewer]</t>
+          <t>11.820 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2329,7 +2281,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGC 14937</t>
+          <t>PGC31027</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2339,7 +2291,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65.333179 36.760135</t>
+          <t>157.750000 78.850000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2349,7 +2301,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.00819901 / 113.09 million ly</t>
+          <t>0.00934980 / 130.60 million ly</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2359,17 +2311,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1.163 × 0.256 arcmin [catalog value; band/isophote may vary]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,458.0 km/s</t>
+          <t>2,789.9 km/s</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>EST [38.3 × 8.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [39.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2384,7 +2336,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2401,7 +2353,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IC273                 UGC2425               MCG0-08-052           CGCG389-52            IRAS02546+0234</t>
+          <t>NGC  3394</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2411,37 +2363,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44.295000 2.775556</t>
+          <t>162.662500 65.727500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.01056965 / 116.80 million ly</t>
+          <t>0.01135119 / 158.56 million ly</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Early spiral / S0-a galaxy [de Vaucouleurs T=0.9]</t>
+          <t>GiP [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1.180 arcmin [catalog value]</t>
+          <t>1.280 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,168.7 km/s</t>
+          <t>3,403.0 km/s</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>EST [40.1 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [59.0 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2456,7 +2408,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2466,14 +2418,14 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>78% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IC1894                CGCG464-6             NPM1G+19.0105</t>
+          <t>PGC23700</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2483,42 +2435,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47.605833 19.606667</t>
+          <t>126.775000 21.650000</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.03493417 / 475.06 million ly</t>
+          <t>0.02529750 / 353.37 million ly</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Lenticular galaxy [de Vaucouleurs T=-2.0]</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.890 arcmin [catalog value]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,473.0 km/s</t>
+          <t>7,584.0 km/s</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>EST [123.0 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [106.9 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>14.100 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2528,7 +2480,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2538,14 +2490,14 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>83% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGC 11640</t>
+          <t>PGC 175756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2555,7 +2507,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46.524666 41.725333</t>
+          <t>45.453333 2.059722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2565,27 +2517,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.01200164 / 170.76 million ly</t>
+          <t>0.10211100 / 1426.33 million ly</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.373 × 0.336 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.520 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,598.0 km/s</t>
+          <t>29,056.5 km/s</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>EST [18.5 × 16.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [215.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2600,7 +2552,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2617,7 +2569,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PGC 1316867</t>
+          <t>PGC 1477525</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2627,7 +2579,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37.859583 7.233056</t>
+          <t>53.344583 15.182778</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2647,7 +2599,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.620 arcmin [catalog value]</t>
+          <t>0.390 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2689,7 +2641,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PGC31098</t>
+          <t>PGC 1512559</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2699,12 +2651,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>157.975000 77.800000</t>
+          <t>58.692083 16.599167</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EST [mixed/younger stellar populations possible, broadly 1–10 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2719,7 +2671,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1.120 arcmin [catalog value]</t>
+          <t>0.420 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2754,14 +2706,14 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>69% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGC 3095597</t>
+          <t>PGC 1397822</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2771,7 +2723,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40.560833 5.510000</t>
+          <t>38.649583 11.723056</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2781,27 +2733,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.06965624 / 972.99 million ly</t>
+          <t>0.02686576 / 375.27 million ly</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sy1 [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0.243 × 0.204 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.880 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,156.8 km/s</t>
+          <t>7,946.0 km/s</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>EST [68.8 × 57.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [96.1 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2936,7 +2888,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PGC31036</t>
+          <t>PGC 90695</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2946,37 +2898,37 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>157.800000 72.100000</t>
+          <t>57.312081 16.084660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.02231210 / 311.67 million ly</t>
+          <t>0.02128372 / 287.88 million ly</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GiG [SIMBAD classification]</t>
+          <t>LSB [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1.130 arcmin [catalog value]</t>
+          <t>0.727 × 0.116 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>6,689.0 km/s</t>
+          <t>6,380.7 km/s</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>EST [102.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [60.9 × 9.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -2991,7 +2943,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>EST [simple Hubble-law distance; verify independently]</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -3008,7 +2960,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PGC 1496412</t>
+          <t>PGC 3096784</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -3018,7 +2970,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57.827500 15.920000</t>
+          <t>37.995000 22.765284</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3028,7 +2980,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>0.03266927 / 448.27 million ly</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3038,17 +2990,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.480 arcmin [catalog value]</t>
+          <t>0.300 × 0.180 arcmin [catalog value; band/isophote may vary]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>9,794.0 km/s</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [39.1 × 23.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -3073,14 +3025,14 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>69% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>78% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NGC  1023</t>
+          <t>NGC  3504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3090,42 +3042,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40.100417 39.062778</t>
+          <t>165.795000 27.973611</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EST [typically old-dominated stellar population, roughly 9–13 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.00200472 / 28.00 million ly</t>
+          <t>0.00506350 / 70.73 million ly</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.940 arcmin [catalog value]</t>
+          <t>1.430 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>601.0 km/s</t>
+          <t>1,518.0 km/s</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>EST [15.8 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [29.4 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10.350 [catalog photometry; band must be shown in viewer]</t>
+          <t>11.820 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -3152,7 +3104,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGC 14937</t>
+          <t>PGC31027</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3162,7 +3114,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65.333179 36.760135</t>
+          <t>157.750000 78.850000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3172,7 +3124,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.00819901 / 113.09 million ly</t>
+          <t>0.00934980 / 130.60 million ly</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3182,17 +3134,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1.163 × 0.256 arcmin [catalog value; band/isophote may vary]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,458.0 km/s</t>
+          <t>2,789.9 km/s</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>EST [38.3 × 8.4 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [39.5 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3207,7 +3159,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3224,7 +3176,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IC273                 UGC2425               MCG0-08-052           CGCG389-52            IRAS02546+0234</t>
+          <t>NGC  3394</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3234,37 +3186,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44.295000 2.775556</t>
+          <t>162.662500 65.727500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.01056965 / 116.80 million ly</t>
+          <t>0.01135119 / 158.56 million ly</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Early spiral / S0-a galaxy [de Vaucouleurs T=0.9]</t>
+          <t>GiP [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1.180 arcmin [catalog value]</t>
+          <t>1.280 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,168.7 km/s</t>
+          <t>3,403.0 km/s</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>EST [40.1 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [59.0 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3279,7 +3231,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -3289,14 +3241,14 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>78% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IC1894                CGCG464-6             NPM1G+19.0105</t>
+          <t>PGC23700</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3306,42 +3258,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47.605833 19.606667</t>
+          <t>126.775000 21.650000</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
+          <t>EST [mixed stellar populations, broadly 5–12 billion years; morphology-based, not a direct measurement]</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.03493417 / 475.06 million ly</t>
+          <t>0.02529750 / 353.37 million ly</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Lenticular galaxy [de Vaucouleurs T=-2.0]</t>
+          <t>LIN [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.890 arcmin [catalog value]</t>
+          <t>1.040 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,473.0 km/s</t>
+          <t>7,584.0 km/s</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>EST [123.0 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [106.9 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>14.100 [catalog photometry; band must be shown in viewer]</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3361,14 +3313,14 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>83% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGC 11640</t>
+          <t>PGC 175756</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3378,7 +3330,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46.524666 41.725333</t>
+          <t>45.453333 2.059722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3388,27 +3340,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.01200164 / 170.76 million ly</t>
+          <t>0.10211100 / 1426.33 million ly</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>AG? [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.373 × 0.336 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.520 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,598.0 km/s</t>
+          <t>29,056.5 km/s</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>EST [18.5 × 16.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [215.7 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3423,7 +3375,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>EST [simple Hubble-law distance; verify independently]</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3440,7 +3392,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PGC 1316867</t>
+          <t>PGC 1477525</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3450,7 +3402,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37.859583 7.233056</t>
+          <t>53.344583 15.182778</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3470,7 +3422,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.620 arcmin [catalog value]</t>
+          <t>0.390 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -3512,7 +3464,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PGC31098</t>
+          <t>PGC 1512559</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3522,12 +3474,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>157.975000 77.800000</t>
+          <t>58.692083 16.599167</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EST [mixed/younger stellar populations possible, broadly 1–10 billion years; morphology-based, not a direct measurement]</t>
+          <t>EST [broad 8–12 billion year population range; not object-specific; verify independently]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3542,7 +3494,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1.120 arcmin [catalog value]</t>
+          <t>0.420 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -3577,14 +3529,14 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60% [completeness + independent agreement + provenance; verify critical values]</t>
+          <t>69% [completeness + independent agreement + provenance; verify critical values]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGC 3095597</t>
+          <t>PGC 1397822</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3594,7 +3546,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40.560833 5.510000</t>
+          <t>38.649583 11.723056</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3604,27 +3556,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.06965624 / 972.99 million ly</t>
+          <t>0.02686576 / 375.27 million ly</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sy1 [SIMBAD classification]</t>
+          <t>G [SIMBAD classification]</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0.243 × 0.204 arcmin [catalog value; band/isophote may vary]</t>
+          <t>0.880 arcmin [catalog value]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,156.8 km/s</t>
+          <t>7,946.0 km/s</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>EST [68.8 × 57.7 thousand ly; derived from adopted distance and angular size]</t>
+          <t>EST [96.1 thousand ly; derived from adopted distance and angular size]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
